--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -188,13 +188,13 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
@@ -956,7 +956,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1033,7 +1033,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -1087,7 +1087,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1264,7 +1264,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1341,7 +1341,7 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -1395,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1495,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1572,7 +1572,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -1626,7 +1626,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1649,7 +1649,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>9</v>
@@ -1703,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1726,7 +1726,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1780,7 +1780,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1803,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -1857,7 +1857,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1880,7 +1880,7 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1934,7 +1934,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -2034,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -2088,7 +2088,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -2165,7 +2165,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2188,7 +2188,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -2242,7 +2242,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2265,7 +2265,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2319,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2419,7 +2419,7 @@
         <v>7</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>10</v>
@@ -2473,7 +2473,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2496,7 +2496,7 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D24">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2573,7 +2573,7 @@
         <v>9</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>10</v>
@@ -2627,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2650,7 +2650,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>9</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2727,7 +2727,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>9</v>
@@ -2781,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2804,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2858,7 +2858,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -2881,7 +2881,7 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -2935,7 +2935,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -2958,7 +2958,7 @@
         <v>10</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -3012,7 +3012,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3035,7 +3035,7 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -3089,7 +3089,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3112,7 +3112,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <v>9</v>
@@ -3166,7 +3166,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3266,7 +3266,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -3320,7 +3320,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3343,7 +3343,7 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -3397,7 +3397,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3621,80 +3621,83 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>38.24</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>8.9</v>
+      </c>
       <c r="I3">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>38.24</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>25.71</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>61.76</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>35</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>68.56999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G5">
-        <v>25.71</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -3705,34 +3708,34 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>74.29000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>5.71</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3774,7 +3777,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3835,7 +3838,7 @@
         <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>56</v>
@@ -3843,22 +3846,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920115</v>
+        <v>20330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3875,87 +3878,87 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920116</v>
+        <v>20330051920118</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920116</v>
+        <v>20330051920119</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920118</v>
+        <v>20330051920119</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920118</v>
+        <v>20330051920119</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -3963,16 +3966,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920119</v>
+        <v>20330051920121</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -3983,79 +3986,79 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920121</v>
+        <v>20330051920122</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920121</v>
+        <v>20330051920122</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
@@ -4075,10 +4078,10 @@
         <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4095,104 +4098,104 @@
         <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920122</v>
+        <v>20330051920123</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920122</v>
+        <v>20330051920125</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920123</v>
+        <v>20330051920126</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -4203,36 +4206,36 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920123</v>
+        <v>20330051920127</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920124</v>
+        <v>20330051920128</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -4243,19 +4246,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920124</v>
+        <v>20330051920128</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>56</v>
@@ -4263,59 +4266,59 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920124</v>
+        <v>20330051920129</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920125</v>
+        <v>20330051920129</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920125</v>
+        <v>20330051920129</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>56</v>
@@ -4323,16 +4326,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920126</v>
+        <v>20330051920131</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -4343,19 +4346,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920126</v>
+        <v>20330051920131</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
         <v>56</v>
@@ -4363,16 +4366,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920127</v>
+        <v>20330051920132</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -4383,36 +4386,36 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920127</v>
+        <v>20330051920133</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920128</v>
+        <v>20330051920134</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -4423,19 +4426,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920128</v>
+        <v>20330051920134</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
         <v>56</v>
@@ -4443,36 +4446,36 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920128</v>
+        <v>20330051920135</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920129</v>
+        <v>20330051920135</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -4483,56 +4486,56 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920129</v>
+        <v>20330051920135</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920129</v>
+        <v>20330051920135</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920131</v>
+        <v>20330051920136</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -4543,19 +4546,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920131</v>
+        <v>20330051920136</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
         <v>56</v>
@@ -4563,36 +4566,36 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920131</v>
+        <v>20330051920137</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920132</v>
+        <v>20330051920139</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -4603,36 +4606,36 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920132</v>
+        <v>19330051920387</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920133</v>
+        <v>20330051920140</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -4643,19 +4646,19 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920133</v>
+        <v>20330051920140</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C44" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>56</v>
@@ -4663,16 +4666,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920134</v>
+        <v>20330051920141</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -4683,19 +4686,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920134</v>
+        <v>20330051920141</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
         <v>56</v>
@@ -4703,116 +4706,116 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920134</v>
+        <v>20330051920389</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920135</v>
+        <v>20330051920142</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920135</v>
+        <v>20330051920142</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920135</v>
+        <v>20330051920143</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="E50" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920135</v>
+        <v>20330051920143</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920136</v>
+        <v>20330051920144</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
@@ -4823,19 +4826,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920136</v>
+        <v>20330051920144</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
         <v>56</v>
@@ -4843,99 +4846,99 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920136</v>
+        <v>20330051920387</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920137</v>
+        <v>20330051920387</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D55" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920137</v>
+        <v>20330051920145</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920139</v>
+        <v>20330051920145</v>
       </c>
       <c r="B57" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F57" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920139</v>
+        <v>20330051920145</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E58" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
         <v>56</v>
@@ -4943,16 +4946,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>19330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="D59" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -4963,19 +4966,19 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>19330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B60" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
         <v>56</v>
@@ -4983,16 +4986,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920140</v>
+        <v>20330051920150</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D61" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -5003,79 +5006,79 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920140</v>
+        <v>20330051920151</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F62" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920140</v>
+        <v>20330051920151</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D63" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920141</v>
+        <v>20330051920151</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E64" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F64" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920141</v>
+        <v>20330051920151</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D65" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
         <v>56</v>
@@ -5083,653 +5086,96 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>20330051920141</v>
+        <v>20330051920153</v>
       </c>
       <c r="B66" t="s">
-        <v>83</v>
-      </c>
-      <c r="C66" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>20330051920389</v>
+        <v>20330051920153</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
-      </c>
-      <c r="C67" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D67" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>20330051920389</v>
+        <v>19330051920145</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D68" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E68" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>20330051920142</v>
+        <v>19330051920145</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E69" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>20330051920142</v>
+        <v>19330051920145</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D70" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920142</v>
-      </c>
-      <c r="B71" t="s">
-        <v>85</v>
-      </c>
-      <c r="C71" t="s">
-        <v>104</v>
-      </c>
-      <c r="D71" t="s">
-        <v>141</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920143</v>
-      </c>
-      <c r="B72" t="s">
-        <v>86</v>
-      </c>
-      <c r="C72" t="s">
-        <v>111</v>
-      </c>
-      <c r="D72" t="s">
-        <v>142</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920143</v>
-      </c>
-      <c r="B73" t="s">
-        <v>86</v>
-      </c>
-      <c r="C73" t="s">
-        <v>111</v>
-      </c>
-      <c r="D73" t="s">
-        <v>142</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920143</v>
-      </c>
-      <c r="B74" t="s">
-        <v>86</v>
-      </c>
-      <c r="C74" t="s">
-        <v>111</v>
-      </c>
-      <c r="D74" t="s">
-        <v>142</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920144</v>
-      </c>
-      <c r="B75" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" t="s">
-        <v>112</v>
-      </c>
-      <c r="D75" t="s">
-        <v>143</v>
-      </c>
-      <c r="E75" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920144</v>
-      </c>
-      <c r="B76" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>143</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920144</v>
-      </c>
-      <c r="B77" t="s">
-        <v>87</v>
-      </c>
-      <c r="C77" t="s">
-        <v>112</v>
-      </c>
-      <c r="D77" t="s">
-        <v>143</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920387</v>
-      </c>
-      <c r="B78" t="s">
-        <v>88</v>
-      </c>
-      <c r="C78" t="s">
-        <v>113</v>
-      </c>
-      <c r="D78" t="s">
-        <v>121</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920387</v>
-      </c>
-      <c r="B79" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" t="s">
-        <v>113</v>
-      </c>
-      <c r="D79" t="s">
-        <v>121</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920387</v>
-      </c>
-      <c r="B80" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" t="s">
-        <v>113</v>
-      </c>
-      <c r="D80" t="s">
-        <v>121</v>
-      </c>
-      <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920145</v>
-      </c>
-      <c r="B81" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" t="s">
-        <v>75</v>
-      </c>
-      <c r="D81" t="s">
-        <v>144</v>
-      </c>
-      <c r="E81" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920145</v>
-      </c>
-      <c r="B82" t="s">
-        <v>89</v>
-      </c>
-      <c r="C82" t="s">
-        <v>75</v>
-      </c>
-      <c r="D82" t="s">
-        <v>144</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920145</v>
-      </c>
-      <c r="B83" t="s">
-        <v>89</v>
-      </c>
-      <c r="C83" t="s">
-        <v>75</v>
-      </c>
-      <c r="D83" t="s">
-        <v>144</v>
-      </c>
-      <c r="E83" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920148</v>
-      </c>
-      <c r="B84" t="s">
-        <v>90</v>
-      </c>
-      <c r="C84" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" t="s">
-        <v>145</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920148</v>
-      </c>
-      <c r="B85" t="s">
-        <v>90</v>
-      </c>
-      <c r="C85" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" t="s">
-        <v>145</v>
-      </c>
-      <c r="E85" t="s">
-        <v>6</v>
-      </c>
-      <c r="F85" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920148</v>
-      </c>
-      <c r="B86" t="s">
-        <v>90</v>
-      </c>
-      <c r="C86" t="s">
-        <v>114</v>
-      </c>
-      <c r="D86" t="s">
-        <v>145</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920150</v>
-      </c>
-      <c r="B87" t="s">
-        <v>91</v>
-      </c>
-      <c r="C87" t="s">
-        <v>115</v>
-      </c>
-      <c r="D87" t="s">
-        <v>146</v>
-      </c>
-      <c r="E87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920150</v>
-      </c>
-      <c r="B88" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" t="s">
-        <v>115</v>
-      </c>
-      <c r="D88" t="s">
-        <v>146</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920151</v>
-      </c>
-      <c r="B89" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" t="s">
-        <v>116</v>
-      </c>
-      <c r="D89" t="s">
-        <v>147</v>
-      </c>
-      <c r="E89" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920151</v>
-      </c>
-      <c r="B90" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90" t="s">
-        <v>116</v>
-      </c>
-      <c r="D90" t="s">
-        <v>147</v>
-      </c>
-      <c r="E90" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920151</v>
-      </c>
-      <c r="B91" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" t="s">
-        <v>116</v>
-      </c>
-      <c r="D91" t="s">
-        <v>147</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920151</v>
-      </c>
-      <c r="B92" t="s">
-        <v>92</v>
-      </c>
-      <c r="C92" t="s">
-        <v>116</v>
-      </c>
-      <c r="D92" t="s">
-        <v>147</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920153</v>
-      </c>
-      <c r="B93" t="s">
-        <v>93</v>
-      </c>
-      <c r="D93" t="s">
-        <v>148</v>
-      </c>
-      <c r="E93" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920153</v>
-      </c>
-      <c r="B94" t="s">
-        <v>93</v>
-      </c>
-      <c r="D94" t="s">
-        <v>148</v>
-      </c>
-      <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920153</v>
-      </c>
-      <c r="B95" t="s">
-        <v>93</v>
-      </c>
-      <c r="D95" t="s">
-        <v>148</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920145</v>
-      </c>
-      <c r="B96" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" t="s">
-        <v>117</v>
-      </c>
-      <c r="D96" t="s">
-        <v>149</v>
-      </c>
-      <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920145</v>
-      </c>
-      <c r="B97" t="s">
-        <v>94</v>
-      </c>
-      <c r="C97" t="s">
-        <v>117</v>
-      </c>
-      <c r="D97" t="s">
-        <v>149</v>
-      </c>
-      <c r="E97" t="s">
-        <v>5</v>
-      </c>
-      <c r="F97" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920145</v>
-      </c>
-      <c r="B98" t="s">
-        <v>94</v>
-      </c>
-      <c r="C98" t="s">
-        <v>117</v>
-      </c>
-      <c r="D98" t="s">
-        <v>149</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5816,16 +5262,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920115</v>
+        <v>20330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5833,16 +5279,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920116</v>
+        <v>20330051920129</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5850,16 +5296,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920119</v>
+        <v>20330051920145</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -5867,16 +5313,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920124</v>
+        <v>19330051920145</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5884,254 +5330,254 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920128</v>
+        <v>20330051920115</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920129</v>
+        <v>20330051920116</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920131</v>
+        <v>20330051920124</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920134</v>
+        <v>20330051920128</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920136</v>
+        <v>20330051920131</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920140</v>
+        <v>20330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920141</v>
+        <v>20330051920136</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920142</v>
+        <v>20330051920140</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920143</v>
+        <v>20330051920141</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920144</v>
+        <v>20330051920142</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920387</v>
+        <v>20330051920143</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920145</v>
+        <v>20330051920144</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920153</v>
+        <v>20330051920148</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920145</v>
+        <v>20330051920153</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6148,7 +5594,7 @@
         <v>120</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6165,7 +5611,7 @@
         <v>122</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6182,7 +5628,7 @@
         <v>124</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6199,7 +5645,7 @@
         <v>126</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6216,7 +5662,7 @@
         <v>127</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6233,7 +5679,7 @@
         <v>128</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6250,7 +5696,7 @@
         <v>132</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6267,7 +5713,7 @@
         <v>133</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6284,7 +5730,7 @@
         <v>136</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6301,7 +5747,7 @@
         <v>137</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -6318,7 +5764,7 @@
         <v>138</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -6335,7 +5781,7 @@
         <v>140</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -6352,7 +5798,7 @@
         <v>146</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6362,7 +5808,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6394,22 +5840,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920118</v>
+        <v>20330051920115</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6417,22 +5863,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920118</v>
+        <v>20330051920115</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6440,22 +5886,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920121</v>
+        <v>20330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6463,22 +5909,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920121</v>
+        <v>20330051920116</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6486,22 +5932,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920123</v>
+        <v>20330051920128</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6509,22 +5955,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920123</v>
+        <v>20330051920128</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6532,22 +5978,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6555,22 +6001,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6578,39 +6024,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920127</v>
+        <v>20330051920132</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920127</v>
+        <v>20330051920132</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -6624,39 +6070,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920139</v>
+        <v>20330051920133</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920139</v>
+        <v>20330051920133</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -6670,22 +6116,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920387</v>
+        <v>20330051920136</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6693,22 +6139,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920387</v>
+        <v>20330051920136</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6716,39 +6162,39 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920389</v>
+        <v>20330051920137</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920389</v>
+        <v>20330051920137</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -6762,22 +6208,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920150</v>
+        <v>20330051920140</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -6785,24 +6231,455 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
+        <v>20330051920140</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920141</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920142</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920142</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920143</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920143</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" t="s">
+        <v>142</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920144</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920153</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920118</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920121</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920123</v>
+      </c>
+      <c r="B32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920125</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>55</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920127</v>
+      </c>
+      <c r="B34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>55</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920139</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>55</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>19330051920387</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920389</v>
+      </c>
+      <c r="B37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>55</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
         <v>20330051920150</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B38" t="s">
         <v>91</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C38" t="s">
         <v>115</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D38" t="s">
         <v>146</v>
       </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
         <v>55</v>
       </c>
-      <c r="G19">
+      <c r="G38">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
@@ -218,256 +218,256 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
     <t>CONGUILLO</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>OLTEHUA</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
     <t>PACHECO</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>TIBURCIO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
     <t>ZOPIYACTLE</t>
   </si>
   <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
     <t>NOYOLA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
     <t>REYNOSO</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
     <t>CONSUELO DALILA</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
     <t>MARIA</t>
   </si>
   <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
     <t>EMELIN JIROMI</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
     <t>AIDA</t>
   </si>
   <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
     <t>ODALYS</t>
   </si>
   <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
     <t>ABDIEL</t>
   </si>
   <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
     <t>VALERIA</t>
   </si>
   <si>
     <t>SANDY SAMARA</t>
   </si>
   <si>
-    <t>KARLA</t>
-  </si>
-  <si>
     <t>TAILY</t>
   </si>
   <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
     <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
   </si>
 </sst>
 </file>
@@ -965,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -1019,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1119,7 +1119,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -1173,7 +1173,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1273,7 +1273,7 @@
         <v>7</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -1327,7 +1327,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1350,7 +1350,7 @@
         <v>9</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -1404,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>-1</v>
@@ -1504,7 +1504,7 @@
         <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>9</v>
@@ -1558,7 +1558,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1658,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -1712,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1812,7 +1812,7 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1866,7 +1866,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1889,7 +1889,7 @@
         <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -1943,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>-1</v>
@@ -1966,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -2020,7 +2020,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>-1</v>
@@ -2043,7 +2043,7 @@
         <v>8</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -2097,7 +2097,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>-1</v>
@@ -2120,7 +2120,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -2174,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2197,7 +2197,7 @@
         <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2251,7 +2251,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2274,7 +2274,7 @@
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -2328,7 +2328,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -2482,7 +2482,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>-1</v>
@@ -2582,7 +2582,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>7</v>
@@ -2636,7 +2636,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2659,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>-1</v>
@@ -2736,7 +2736,7 @@
         <v>9</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -2790,7 +2790,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2890,7 +2890,7 @@
         <v>9</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -2944,7 +2944,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -2967,7 +2967,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -3021,7 +3021,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -3044,7 +3044,7 @@
         <v>9</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>-1</v>
@@ -3098,7 +3098,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3198,7 +3198,7 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G33">
         <v>-1</v>
@@ -3252,7 +3252,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>-1</v>
@@ -3352,7 +3352,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G35">
         <v>10</v>
@@ -3406,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3592,27 +3592,30 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>38.24</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.9</v>
+      </c>
       <c r="I2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3621,25 +3624,25 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>38.24</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>61.76</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3777,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3812,16 +3815,16 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3832,16 +3835,16 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3852,13 +3855,13 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -3866,19 +3869,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920116</v>
+        <v>20330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>56</v>
@@ -3886,22 +3889,22 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920118</v>
+        <v>20330051920119</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3909,16 +3912,16 @@
         <v>20330051920119</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -3926,39 +3929,39 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -3966,22 +3969,22 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920121</v>
+        <v>20330051920122</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3989,19 +3992,19 @@
         <v>20330051920122</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4009,19 +4012,19 @@
         <v>20330051920122</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4029,36 +4032,36 @@
         <v>20330051920122</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
@@ -4066,59 +4069,59 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920122</v>
+        <v>20330051920126</v>
       </c>
       <c r="B16" t="s">
         <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920123</v>
+        <v>20330051920128</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>55</v>
@@ -4126,59 +4129,59 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920124</v>
+        <v>20330051920129</v>
       </c>
       <c r="B18" t="s">
         <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920124</v>
+        <v>20330051920129</v>
       </c>
       <c r="B19" t="s">
         <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>55</v>
@@ -4186,19 +4189,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920126</v>
+        <v>20330051920134</v>
       </c>
       <c r="B21" t="s">
         <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>55</v>
@@ -4206,79 +4209,79 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920127</v>
+        <v>20330051920135</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920128</v>
+        <v>20330051920135</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920128</v>
+        <v>20330051920135</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920129</v>
+        <v>20330051920135</v>
       </c>
       <c r="B25" t="s">
         <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>55</v>
@@ -4286,39 +4289,39 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920129</v>
+        <v>20330051920136</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920129</v>
+        <v>20330051920137</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
         <v>56</v>
@@ -4326,19 +4329,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920131</v>
+        <v>20330051920140</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
         <v>55</v>
@@ -4346,19 +4349,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920131</v>
+        <v>20330051920141</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>56</v>
@@ -4366,19 +4369,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920132</v>
+        <v>20330051920141</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
         <v>55</v>
@@ -4386,19 +4389,19 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920133</v>
+        <v>20330051920142</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
         <v>55</v>
@@ -4406,19 +4409,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920134</v>
+        <v>20330051920143</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
         <v>55</v>
@@ -4426,59 +4429,59 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920134</v>
+        <v>20330051920144</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920135</v>
+        <v>20330051920387</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920135</v>
+        <v>20330051920387</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
         <v>55</v>
@@ -4486,16 +4489,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920135</v>
+        <v>20330051920145</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
@@ -4506,139 +4509,139 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920135</v>
+        <v>20330051920145</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920136</v>
+        <v>20330051920148</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920136</v>
+        <v>20330051920148</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920137</v>
+        <v>20330051920151</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920139</v>
+        <v>20330051920151</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920387</v>
+        <v>20330051920151</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920140</v>
+        <v>20330051920151</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
         <v>55</v>
@@ -4646,535 +4649,78 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920140</v>
+        <v>20330051920153</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D44" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920141</v>
+        <v>19330051920145</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D45" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920141</v>
+        <v>19330051920145</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920389</v>
+        <v>19330051920145</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920142</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920142</v>
-      </c>
-      <c r="B49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920143</v>
-      </c>
-      <c r="B50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" t="s">
-        <v>111</v>
-      </c>
-      <c r="D50" t="s">
-        <v>142</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920143</v>
-      </c>
-      <c r="B51" t="s">
-        <v>86</v>
-      </c>
-      <c r="C51" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" t="s">
-        <v>142</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920144</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920144</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D53" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920387</v>
-      </c>
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" t="s">
-        <v>121</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920387</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" t="s">
-        <v>121</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920145</v>
-      </c>
-      <c r="B56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" t="s">
-        <v>75</v>
-      </c>
-      <c r="D56" t="s">
-        <v>144</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920145</v>
-      </c>
-      <c r="B57" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" t="s">
-        <v>144</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920145</v>
-      </c>
-      <c r="B58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" t="s">
-        <v>144</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920148</v>
-      </c>
-      <c r="B59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" t="s">
-        <v>145</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920148</v>
-      </c>
-      <c r="B60" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" t="s">
-        <v>145</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920150</v>
-      </c>
-      <c r="B61" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
-        <v>115</v>
-      </c>
-      <c r="D61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920151</v>
-      </c>
-      <c r="B62" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" t="s">
-        <v>116</v>
-      </c>
-      <c r="D62" t="s">
-        <v>147</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920151</v>
-      </c>
-      <c r="B63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" t="s">
-        <v>116</v>
-      </c>
-      <c r="D63" t="s">
-        <v>147</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920151</v>
-      </c>
-      <c r="B64" t="s">
-        <v>92</v>
-      </c>
-      <c r="C64" t="s">
-        <v>116</v>
-      </c>
-      <c r="D64" t="s">
-        <v>147</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920151</v>
-      </c>
-      <c r="B65" t="s">
-        <v>92</v>
-      </c>
-      <c r="C65" t="s">
-        <v>116</v>
-      </c>
-      <c r="D65" t="s">
-        <v>147</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920153</v>
-      </c>
-      <c r="B66" t="s">
-        <v>93</v>
-      </c>
-      <c r="D66" t="s">
-        <v>148</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920153</v>
-      </c>
-      <c r="B67" t="s">
-        <v>93</v>
-      </c>
-      <c r="D67" t="s">
-        <v>148</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920145</v>
-      </c>
-      <c r="B68" t="s">
-        <v>94</v>
-      </c>
-      <c r="C68" t="s">
-        <v>117</v>
-      </c>
-      <c r="D68" t="s">
-        <v>149</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920145</v>
-      </c>
-      <c r="B69" t="s">
-        <v>94</v>
-      </c>
-      <c r="C69" t="s">
-        <v>117</v>
-      </c>
-      <c r="D69" t="s">
-        <v>149</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920145</v>
-      </c>
-      <c r="B70" t="s">
-        <v>94</v>
-      </c>
-      <c r="C70" t="s">
-        <v>117</v>
-      </c>
-      <c r="D70" t="s">
-        <v>149</v>
-      </c>
-      <c r="E70" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5214,13 +4760,13 @@
         <v>20330051920122</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -5231,13 +4777,13 @@
         <v>20330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5248,13 +4794,13 @@
         <v>20330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5265,13 +4811,13 @@
         <v>20330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5279,16 +4825,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920129</v>
+        <v>19330051920145</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5296,50 +4842,50 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920145</v>
+        <v>20330051920115</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920145</v>
+        <v>20330051920124</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920115</v>
+        <v>20330051920129</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -5347,13 +4893,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920116</v>
+        <v>20330051920141</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>119</v>
@@ -5364,16 +4910,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920124</v>
+        <v>20330051920387</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -5381,16 +4927,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920128</v>
+        <v>20330051920145</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5398,16 +4944,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920131</v>
+        <v>20330051920148</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5415,183 +4961,186 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920134</v>
+        <v>20330051920116</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920136</v>
+        <v>20330051920126</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920140</v>
+        <v>20330051920128</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920141</v>
+        <v>20330051920131</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920142</v>
+        <v>20330051920134</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920143</v>
+        <v>20330051920136</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920144</v>
+        <v>20330051920137</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920148</v>
+        <v>20330051920142</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920153</v>
+        <v>20330051920143</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920118</v>
+        <v>20330051920144</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5599,16 +5148,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920121</v>
+        <v>20330051920153</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -5616,121 +5162,121 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920123</v>
+        <v>20330051920118</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920125</v>
+        <v>20330051920121</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920126</v>
+        <v>20330051920123</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920127</v>
+        <v>20330051920125</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920132</v>
+        <v>20330051920127</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920133</v>
+        <v>20330051920132</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920137</v>
+        <v>20330051920133</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5738,16 +5284,16 @@
         <v>20330051920139</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -5755,16 +5301,16 @@
         <v>19330051920387</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5772,16 +5318,16 @@
         <v>20330051920389</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5789,16 +5335,16 @@
         <v>20330051920150</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5808,7 +5354,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5846,16 +5392,16 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5869,16 +5415,16 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5886,22 +5432,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920116</v>
+        <v>20330051920129</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5909,22 +5455,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920116</v>
+        <v>20330051920129</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5932,45 +5478,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920128</v>
+        <v>20330051920134</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920128</v>
+        <v>20330051920134</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5978,42 +5524,42 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920131</v>
+        <v>20330051920137</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920131</v>
+        <v>20330051920137</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -6024,42 +5570,42 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920132</v>
+        <v>20330051920141</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920132</v>
+        <v>20330051920141</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
@@ -6070,42 +5616,42 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920133</v>
+        <v>20330051920145</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920133</v>
+        <v>20330051920145</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
@@ -6116,19 +5662,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920136</v>
+        <v>20330051920116</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>55</v>
@@ -6139,22 +5685,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920136</v>
+        <v>20330051920128</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6162,91 +5708,91 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920137</v>
+        <v>20330051920131</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920137</v>
+        <v>20330051920132</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920140</v>
+        <v>20330051920133</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920140</v>
+        <v>20330051920136</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -6254,19 +5800,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920141</v>
+        <v>20330051920140</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
         <v>109</v>
       </c>
-      <c r="D20" t="s">
-        <v>139</v>
-      </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>55</v>
@@ -6277,22 +5823,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920141</v>
+        <v>20330051920142</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -6300,19 +5846,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920142</v>
+        <v>20330051920143</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
         <v>55</v>
@@ -6323,22 +5869,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920142</v>
+        <v>20330051920144</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -6346,340 +5892,21 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920143</v>
+        <v>20330051920153</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>55</v>
       </c>
       <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920143</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" t="s">
-        <v>142</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920144</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920144</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920153</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920153</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920118</v>
-      </c>
-      <c r="B30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920121</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920123</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920125</v>
-      </c>
-      <c r="B33" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>55</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920127</v>
-      </c>
-      <c r="B34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920139</v>
-      </c>
-      <c r="B35" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>19330051920387</v>
-      </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920389</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>55</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920150</v>
-      </c>
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" t="s">
-        <v>146</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -215,22 +215,133 @@
     <t>CASTELLANOS</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
   </si>
   <si>
     <t>LIMON</t>
@@ -239,19 +350,13 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
+    <t>OLTEHUA</t>
   </si>
   <si>
     <t>OLIVARES</t>
   </si>
   <si>
-    <t>OSORIO</t>
+    <t>PACHECO</t>
   </si>
   <si>
     <t>RIVERA</t>
@@ -263,61 +368,40 @@
     <t>DE LA ROSA</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>TIBURCIO</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
     <t>BASILIO</t>
   </si>
   <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
   </si>
   <si>
     <t>BARRAGAN</t>
@@ -326,58 +410,49 @@
     <t>CASTRO</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>AMARANTA DENISSE</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
   </si>
   <si>
     <t>KIMBERLY ALONDRA</t>
   </si>
   <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
     <t>MARIJOSE</t>
   </si>
   <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
     <t>GERMAN ERNESTO</t>
   </si>
   <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
   </si>
   <si>
     <t>INGRID YALITH</t>
@@ -389,85 +464,10 @@
     <t>ALONDRA</t>
   </si>
   <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
+    <t>DIANA VIANNEY</t>
   </si>
   <si>
     <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -968,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1045,7 +1045,7 @@
         <v>-1</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1099,7 +1099,7 @@
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1199,7 +1199,7 @@
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1253,7 +1253,7 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1353,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1407,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1584,7 +1584,7 @@
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1638,7 +1638,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1892,7 +1892,7 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1946,7 +1946,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1969,7 +1969,7 @@
         <v>7</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2023,7 +2023,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2046,7 +2046,7 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2100,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2354,7 +2354,7 @@
         <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2408,7 +2408,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2431,7 +2431,7 @@
         <v>8</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2485,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2662,7 +2662,7 @@
         <v>7</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2716,7 +2716,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2816,7 +2816,7 @@
         <v>-1</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2870,7 +2870,7 @@
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2970,7 +2970,7 @@
         <v>9</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3024,7 +3024,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3047,7 +3047,7 @@
         <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3101,7 +3101,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3124,7 +3124,7 @@
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3178,7 +3178,7 @@
         <v>-1</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3201,7 +3201,7 @@
         <v>6</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3255,7 +3255,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3486,7 +3486,7 @@
         <v>-1</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3583,7 +3583,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3592,83 +3592,83 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>38.24</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>61.76</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>67.65000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25.71</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>32.35</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>35</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>68.56999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G4">
-        <v>25.71</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -3679,39 +3679,39 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>74.29000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>5.71</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3720,25 +3720,25 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>17.65</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3780,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3815,33 +3815,33 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920115</v>
+        <v>20330051920119</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -3849,82 +3849,82 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920116</v>
+        <v>20330051920119</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3932,19 +3932,19 @@
         <v>20330051920122</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3952,16 +3952,16 @@
         <v>20330051920122</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -3972,36 +3972,36 @@
         <v>20330051920122</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
@@ -4009,39 +4009,39 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920122</v>
+        <v>20330051920126</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920122</v>
+        <v>20330051920129</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>57</v>
@@ -4049,39 +4049,39 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920124</v>
+        <v>20330051920135</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920124</v>
+        <v>20330051920135</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>55</v>
@@ -4089,79 +4089,79 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920126</v>
+        <v>20330051920135</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920128</v>
+        <v>20330051920136</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920129</v>
+        <v>20330051920137</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920129</v>
+        <v>20330051920141</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>55</v>
@@ -4169,19 +4169,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920131</v>
+        <v>20330051920387</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" t="s">
         <v>93</v>
       </c>
-      <c r="D20" t="s">
-        <v>115</v>
-      </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>55</v>
@@ -4189,99 +4189,99 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920134</v>
+        <v>20330051920145</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920135</v>
+        <v>20330051920148</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920135</v>
+        <v>20330051920148</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920135</v>
+        <v>20330051920151</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920135</v>
+        <v>20330051920151</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
         <v>55</v>
@@ -4289,439 +4289,82 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920136</v>
+        <v>20330051920151</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920137</v>
+        <v>19330051920145</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920140</v>
+        <v>19330051920145</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920141</v>
+        <v>19330051920145</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920141</v>
-      </c>
-      <c r="B30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920142</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920143</v>
-      </c>
-      <c r="B32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920144</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>122</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920387</v>
-      </c>
-      <c r="B34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>109</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920387</v>
-      </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920145</v>
-      </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920145</v>
-      </c>
-      <c r="B37" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920148</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920148</v>
-      </c>
-      <c r="B39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920151</v>
-      </c>
-      <c r="B40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920151</v>
-      </c>
-      <c r="B41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" t="s">
-        <v>105</v>
-      </c>
-      <c r="D41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920151</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" t="s">
-        <v>125</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920151</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920153</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920145</v>
-      </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920145</v>
-      </c>
-      <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920145</v>
-      </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4760,13 +4403,13 @@
         <v>20330051920122</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -4777,16 +4420,16 @@
         <v>20330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4794,30 +4437,30 @@
         <v>20330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920119</v>
+        <v>19330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4825,33 +4468,33 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920145</v>
+        <v>20330051920119</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920115</v>
+        <v>20330051920148</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4859,118 +4502,118 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920124</v>
+        <v>20330051920115</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920129</v>
+        <v>20330051920124</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920141</v>
+        <v>20330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920387</v>
+        <v>20330051920129</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920145</v>
+        <v>20330051920136</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920148</v>
+        <v>20330051920137</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920116</v>
+        <v>20330051920141</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4978,16 +4621,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920126</v>
+        <v>20330051920387</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4995,16 +4638,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920128</v>
+        <v>20330051920145</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5012,166 +4655,169 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920131</v>
+        <v>20330051920116</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920134</v>
+        <v>20330051920118</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920136</v>
+        <v>20330051920121</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920137</v>
+        <v>20330051920123</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920140</v>
+        <v>20330051920125</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920142</v>
+        <v>20330051920127</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920143</v>
+        <v>20330051920128</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920144</v>
+        <v>20330051920131</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920153</v>
+        <v>20330051920132</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920118</v>
+        <v>20330051920133</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5179,16 +4825,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920121</v>
+        <v>20330051920134</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5196,16 +4842,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920123</v>
+        <v>20330051920139</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5213,16 +4859,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920125</v>
+        <v>19330051920387</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5230,16 +4876,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920127</v>
+        <v>20330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5247,13 +4893,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920132</v>
+        <v>20330051920389</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -5264,13 +4910,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920133</v>
+        <v>20330051920142</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -5281,13 +4927,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920139</v>
+        <v>20330051920143</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -5298,13 +4944,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920387</v>
+        <v>20330051920144</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -5315,13 +4961,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920389</v>
+        <v>20330051920150</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -5332,13 +4978,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920150</v>
+        <v>20330051920153</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -5354,7 +4997,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5386,42 +5029,42 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920115</v>
+        <v>20330051920137</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920115</v>
+        <v>20330051920137</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -5432,22 +5075,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920129</v>
+        <v>20330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5455,45 +5098,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920129</v>
+        <v>20330051920141</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920134</v>
+        <v>20330051920387</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5501,19 +5144,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920134</v>
+        <v>20330051920387</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -5524,45 +5167,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920137</v>
+        <v>20330051920115</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920137</v>
+        <v>20330051920129</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
         <v>97</v>
       </c>
-      <c r="D9" t="s">
-        <v>118</v>
-      </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5570,91 +5213,91 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920141</v>
+        <v>20330051920132</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920141</v>
+        <v>20330051920133</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920145</v>
+        <v>20330051920134</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920145</v>
+        <v>20330051920136</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -5662,251 +5305,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920116</v>
+        <v>20330051920145</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920128</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920131</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920132</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920133</v>
-      </c>
-      <c r="B18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920136</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920140</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920142</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920143</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920144</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920153</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -233,217 +233,217 @@
     <t>MARROQUIN</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MARCIAL</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
   </si>
   <si>
     <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -977,7 +977,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1013,7 +1013,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1054,7 +1054,7 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1090,7 +1090,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1131,7 +1131,7 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1187,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -1208,7 +1208,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1241,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1285,7 +1285,7 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1321,7 +1321,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1516,7 +1516,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1593,7 +1593,7 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1670,7 +1670,7 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1706,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1901,7 +1901,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1978,7 +1978,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2055,7 +2055,7 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2209,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2245,7 +2245,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2277,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2286,7 +2286,7 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2322,7 +2322,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2331,7 +2331,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2440,7 +2440,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2517,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2553,7 +2553,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2594,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2671,7 +2671,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2748,7 +2748,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2825,7 +2825,7 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2938,7 +2938,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2958,7 +2958,7 @@
         <v>10</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -2979,7 +2979,7 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3012,7 +3012,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3056,7 +3056,7 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3092,7 +3092,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3133,7 +3133,7 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3169,7 +3169,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3210,7 +3210,7 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3246,7 +3246,7 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3364,7 +3364,7 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3423,7 +3423,7 @@
         <v>-1</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -3441,7 +3441,7 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3477,7 +3477,7 @@
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3688,25 +3688,25 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3720,13 +3720,13 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G6">
         <v>5.88</v>
@@ -3735,10 +3735,10 @@
         <v>8.6</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3752,25 +3752,25 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
   </sheetData>
@@ -3780,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3818,7 +3818,7 @@
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3838,7 +3838,7 @@
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3875,16 +3875,16 @@
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3895,16 +3895,16 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3915,16 +3915,16 @@
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3935,16 +3935,16 @@
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3955,13 +3955,13 @@
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -3969,36 +3969,36 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920122</v>
+        <v>20330051920124</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920124</v>
+        <v>20330051920126</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -4009,42 +4009,42 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920126</v>
+        <v>20330051920129</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920129</v>
+        <v>20330051920135</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4055,16 +4055,16 @@
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4075,24 +4075,24 @@
         <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920135</v>
+        <v>20330051920137</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>83</v>
@@ -4101,44 +4101,44 @@
         <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920136</v>
+        <v>20330051920141</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
         <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920137</v>
+        <v>20330051920387</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -4149,36 +4149,36 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920141</v>
+        <v>20330051920145</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
         <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -4189,36 +4189,36 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920145</v>
+        <v>20330051920148</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B22" t="s">
         <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -4229,36 +4229,36 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B23" t="s">
         <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920151</v>
+        <v>19330051920145</v>
       </c>
       <c r="B24" t="s">
         <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -4269,101 +4269,41 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920151</v>
+        <v>19330051920145</v>
       </c>
       <c r="B25" t="s">
         <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920151</v>
+        <v>19330051920145</v>
       </c>
       <c r="B26" t="s">
         <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920145</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920145</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920145</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4406,10 +4346,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -4423,10 +4363,10 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -4434,16 +4374,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920151</v>
+        <v>19330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -4451,33 +4391,33 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920145</v>
+        <v>20330051920148</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920119</v>
+        <v>20330051920151</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4485,33 +4425,33 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920148</v>
+        <v>20330051920115</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920115</v>
+        <v>20330051920119</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4525,10 +4465,10 @@
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4542,10 +4482,10 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4559,10 +4499,10 @@
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4570,16 +4510,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920136</v>
+        <v>20330051920137</v>
       </c>
       <c r="B12" t="s">
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4587,16 +4527,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920137</v>
+        <v>20330051920141</v>
       </c>
       <c r="B13" t="s">
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4604,16 +4544,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920141</v>
+        <v>20330051920387</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4621,16 +4561,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920387</v>
+        <v>20330051920145</v>
       </c>
       <c r="B15" t="s">
         <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4638,30 +4578,30 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920145</v>
+        <v>20330051920116</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920116</v>
+        <v>20330051920118</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
         <v>131</v>
@@ -4672,13 +4612,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920118</v>
+        <v>20330051920121</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
         <v>132</v>
@@ -4689,10 +4629,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920121</v>
+        <v>20330051920123</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
         <v>119</v>
@@ -4706,13 +4646,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920123</v>
+        <v>20330051920125</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4723,10 +4663,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920125</v>
+        <v>20330051920127</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -4740,13 +4680,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920127</v>
+        <v>20330051920128</v>
       </c>
       <c r="B22" t="s">
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4757,10 +4697,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920128</v>
+        <v>20330051920131</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
         <v>121</v>
@@ -4774,10 +4714,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920131</v>
+        <v>20330051920132</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
         <v>122</v>
@@ -4791,10 +4731,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920132</v>
+        <v>20330051920133</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
         <v>123</v>
@@ -4808,10 +4748,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
         <v>124</v>
@@ -4825,13 +4765,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920134</v>
+        <v>20330051920136</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4845,10 +4785,10 @@
         <v>20330051920139</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4862,7 +4802,7 @@
         <v>19330051920387</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
         <v>67</v>
@@ -4879,13 +4819,13 @@
         <v>20330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4896,10 +4836,10 @@
         <v>20330051920389</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -4913,10 +4853,10 @@
         <v>20330051920142</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -4930,10 +4870,10 @@
         <v>20330051920143</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4947,10 +4887,10 @@
         <v>20330051920144</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -4964,10 +4904,10 @@
         <v>20330051920150</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -4981,7 +4921,7 @@
         <v>20330051920153</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -4997,7 +4937,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5032,13 +4972,13 @@
         <v>20330051920137</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5055,13 +4995,13 @@
         <v>20330051920137</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5078,13 +5018,13 @@
         <v>20330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5101,13 +5041,13 @@
         <v>20330051920141</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5124,13 +5064,13 @@
         <v>20330051920387</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5147,13 +5087,13 @@
         <v>20330051920387</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5176,7 +5116,7 @@
         <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5196,10 +5136,10 @@
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5216,13 +5156,13 @@
         <v>20330051920132</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5239,13 +5179,13 @@
         <v>20330051920133</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -5262,13 +5202,13 @@
         <v>20330051920134</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5282,47 +5222,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920136</v>
+        <v>20330051920145</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
         <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920145</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -212,259 +212,259 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>CUATRA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
   </si>
   <si>
     <t>MAYAHUA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>TIBURCIO</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SUAREZ</t>
   </si>
   <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
   </si>
   <si>
     <t>XOCHIQUISQUI</t>
   </si>
   <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMON</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
     <t>MELANIE NAOMI</t>
   </si>
   <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>JAVIER</t>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
   </si>
   <si>
     <t>ITZEL</t>
   </si>
   <si>
-    <t>ESMERALDA</t>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
   </si>
   <si>
     <t>YAZMIN</t>
   </si>
   <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
     <t>DAMARIS</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
     <t>KARLA</t>
   </si>
   <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
     <t>XIMENA MICHELL</t>
   </si>
   <si>
-    <t>MEILYN ADABEL</t>
+    <t>DIANA VIANNEY</t>
   </si>
   <si>
     <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -971,19 +971,19 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1010,13 +1010,13 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1042,25 +1042,25 @@
         <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1084,19 +1084,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1125,19 +1125,19 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1196,25 +1196,25 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1250,7 +1250,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1279,19 +1279,19 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1324,10 +1324,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1356,19 +1356,19 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1392,7 +1392,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1401,10 +1401,10 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1415,37 +1415,37 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G10">
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1469,19 +1469,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>-1</v>
@@ -1510,19 +1510,19 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1546,7 +1546,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1581,25 +1581,25 @@
         <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1623,19 +1623,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1664,19 +1664,19 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1700,10 +1700,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1712,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1735,25 +1735,25 @@
         <v>5</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1780,16 +1780,16 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1818,19 +1818,19 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1857,13 +1857,13 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1895,19 +1895,19 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1931,7 +1931,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1957,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -1972,19 +1972,19 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2008,19 +2008,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2049,19 +2049,19 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2085,7 +2085,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2094,10 +2094,10 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2126,19 +2126,19 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2165,7 +2165,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2174,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2203,19 +2203,19 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2248,7 +2248,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2280,19 +2280,19 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2325,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2342,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>-1</v>
@@ -2351,25 +2351,25 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2405,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2434,19 +2434,19 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2473,16 +2473,16 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>10</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2505,25 +2505,25 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2547,19 +2547,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2588,19 +2588,19 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2636,7 +2636,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2665,19 +2665,19 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2742,19 +2742,19 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2787,10 +2787,10 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2813,25 +2813,25 @@
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2855,7 +2855,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2864,10 +2864,10 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2896,19 +2896,19 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2941,10 +2941,10 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -2973,19 +2973,19 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3021,7 +3021,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3050,19 +3050,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3089,16 +3089,16 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>10</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3121,25 +3121,25 @@
         <v>5</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3163,19 +3163,19 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>8</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3189,7 +3189,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -3204,19 +3204,19 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3240,19 +3240,19 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>8</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3275,25 +3275,25 @@
         <v>6</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G34">
         <v>-1</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3317,19 +3317,19 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>6</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
         <v>-1</v>
@@ -3358,19 +3358,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3406,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3420,7 +3420,7 @@
         <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -3429,25 +3429,25 @@
         <v>5</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G36">
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3474,7 +3474,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3483,7 +3483,7 @@
         <v>5</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3494,22 +3494,22 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>-1</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3521,13 +3521,13 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3592,30 +3592,30 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>70.59</v>
+      </c>
+      <c r="G2">
+        <v>29.41</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.7</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>32.35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3624,30 +3624,30 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>68.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G3">
-        <v>25.71</v>
+        <v>14.29</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3656,30 +3656,30 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>14.29</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3688,30 +3688,30 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="H5">
         <v>8.6</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3720,25 +3720,25 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G6">
-        <v>5.88</v>
+        <v>8.82</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3780,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3809,56 +3809,56 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920115</v>
+        <v>20330051920122</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920122</v>
+        <v>20330051920135</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3869,442 +3869,42 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920122</v>
+        <v>20330051920148</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920122</v>
+        <v>19330051920145</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920122</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920122</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920122</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920124</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920126</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920129</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920135</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920135</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920135</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920137</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920141</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920387</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920145</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920148</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920148</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920151</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920151</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920145</v>
-      </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920145</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920145</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4343,16 +3943,16 @@
         <v>20330051920122</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4360,234 +3960,234 @@
         <v>20330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920145</v>
+        <v>20330051920148</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920148</v>
+        <v>19330051920145</v>
       </c>
       <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
         <v>75</v>
       </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920151</v>
+        <v>20330051920115</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920115</v>
+        <v>20330051920116</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920119</v>
+        <v>20330051920118</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920124</v>
+        <v>20330051920119</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920126</v>
+        <v>20330051920121</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920129</v>
+        <v>20330051920123</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920137</v>
+        <v>20330051920124</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920141</v>
+        <v>20330051920125</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920387</v>
+        <v>20330051920126</v>
       </c>
       <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
         <v>73</v>
       </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920145</v>
+        <v>20330051920127</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920116</v>
+        <v>20330051920128</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4595,16 +4195,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920118</v>
+        <v>20330051920129</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4612,16 +4212,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920121</v>
+        <v>20330051920131</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4629,16 +4229,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920123</v>
+        <v>20330051920132</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4646,16 +4246,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920125</v>
+        <v>20330051920133</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4663,16 +4263,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920127</v>
+        <v>20330051920134</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4680,16 +4280,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920128</v>
+        <v>20330051920136</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4697,16 +4297,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920131</v>
+        <v>20330051920137</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4714,16 +4314,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920132</v>
+        <v>20330051920139</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4731,16 +4331,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920133</v>
+        <v>19330051920387</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4748,16 +4348,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920134</v>
+        <v>20330051920140</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4765,13 +4365,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920136</v>
+        <v>20330051920141</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4782,13 +4382,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920139</v>
+        <v>20330051920389</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4799,13 +4399,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920387</v>
+        <v>20330051920142</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4816,16 +4416,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920140</v>
+        <v>20330051920143</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4833,16 +4433,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920389</v>
+        <v>20330051920144</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4850,16 +4450,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920142</v>
+        <v>20330051920387</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4867,13 +4467,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920143</v>
+        <v>20330051920145</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4884,13 +4484,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920144</v>
+        <v>20330051920150</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -4901,13 +4501,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920150</v>
+        <v>20330051920151</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -4921,7 +4521,7 @@
         <v>20330051920153</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -4937,7 +4537,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4969,19 +4569,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920137</v>
+        <v>20330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -4992,16 +4592,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920137</v>
+        <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5010,50 +4610,50 @@
         <v>55</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920141</v>
+        <v>20330051920132</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920141</v>
+        <v>20330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5061,22 +4661,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920387</v>
+        <v>20330051920141</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5084,91 +4684,91 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920387</v>
+        <v>20330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920115</v>
+        <v>20330051920145</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920129</v>
+        <v>20330051920145</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920132</v>
+        <v>20330051920148</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5176,45 +4776,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920133</v>
+        <v>20330051920148</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920134</v>
+        <v>20330051920129</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5222,24 +4822,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920145</v>
+        <v>20330051920387</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920145</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,247 +218,247 @@
     <t>MARROQUIN</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
   </si>
   <si>
     <t>RAMON</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
   </si>
   <si>
     <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
   </si>
   <si>
     <t>DIANA VIANNEY</t>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1063,7 +1063,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1294,7 +1294,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1525,7 +1525,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1638,7 +1638,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1679,7 +1679,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1756,7 +1756,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1792,7 +1792,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1833,7 +1833,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1910,7 +1910,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2064,7 +2064,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2218,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2526,7 +2526,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2603,7 +2603,7 @@
         <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2639,7 +2639,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2680,7 +2680,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2757,7 +2757,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2834,7 +2834,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2870,7 +2870,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2911,7 +2911,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2988,7 +2988,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3142,7 +3142,7 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3219,7 +3219,7 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3255,7 +3255,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3278,7 +3278,7 @@
         <v>4</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H34">
         <v>8</v>
@@ -3332,7 +3332,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3373,7 +3373,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3688,89 +3688,89 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G5">
-        <v>5.88</v>
+        <v>8.82</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>91.43000000000001</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>91.18000000000001</v>
-      </c>
-      <c r="G6">
-        <v>8.82</v>
-      </c>
-      <c r="H6">
-        <v>8.1</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
       <c r="J6">
-        <v>0</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>91.43000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H7">
         <v>8.699999999999999</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>8.57</v>
+        <v>2.94</v>
       </c>
     </row>
   </sheetData>
@@ -3780,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3815,16 +3815,16 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3835,16 +3835,16 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3855,56 +3855,36 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920148</v>
+        <v>19330051920145</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920145</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3946,10 +3926,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3963,10 +3943,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3974,16 +3954,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920148</v>
+        <v>19330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3991,30 +3971,30 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920145</v>
+        <v>20330051920115</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920115</v>
+        <v>20330051920116</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
         <v>122</v>
@@ -4025,13 +4005,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920116</v>
+        <v>20330051920118</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>123</v>
@@ -4042,13 +4022,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920118</v>
+        <v>20330051920119</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
         <v>124</v>
@@ -4059,13 +4039,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920119</v>
+        <v>20330051920121</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
         <v>125</v>
@@ -4076,13 +4056,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920121</v>
+        <v>20330051920123</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
         <v>126</v>
@@ -4093,13 +4073,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920123</v>
+        <v>20330051920124</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
         <v>127</v>
@@ -4110,13 +4090,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920124</v>
+        <v>20330051920125</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
         <v>128</v>
@@ -4127,16 +4107,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920125</v>
+        <v>20330051920126</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4144,16 +4124,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920126</v>
+        <v>20330051920127</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4161,13 +4141,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920127</v>
+        <v>20330051920128</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
         <v>130</v>
@@ -4178,13 +4158,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920128</v>
+        <v>20330051920129</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -4195,13 +4175,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920129</v>
+        <v>20330051920131</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -4212,13 +4192,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920131</v>
+        <v>20330051920132</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4229,13 +4209,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920132</v>
+        <v>20330051920133</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -4246,13 +4226,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>135</v>
@@ -4263,13 +4243,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920134</v>
+        <v>20330051920136</v>
       </c>
       <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
         <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
@@ -4280,13 +4260,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920136</v>
+        <v>20330051920137</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
         <v>137</v>
@@ -4297,13 +4277,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920137</v>
+        <v>20330051920139</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
         <v>138</v>
@@ -4314,13 +4294,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>139</v>
@@ -4331,16 +4311,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4348,16 +4328,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920140</v>
+        <v>20330051920141</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4365,13 +4345,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920141</v>
+        <v>20330051920389</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4382,13 +4362,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920389</v>
+        <v>20330051920142</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4399,13 +4379,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920142</v>
+        <v>20330051920143</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4416,13 +4396,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920143</v>
+        <v>20330051920144</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4433,16 +4413,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920144</v>
+        <v>20330051920387</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4450,16 +4430,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920387</v>
+        <v>20330051920145</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4467,13 +4447,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920145</v>
+        <v>20330051920148</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4487,10 +4467,10 @@
         <v>20330051920150</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -4504,10 +4484,10 @@
         <v>20330051920151</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -4521,7 +4501,7 @@
         <v>20330051920153</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -4537,7 +4517,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4572,13 +4552,13 @@
         <v>20330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4595,13 +4575,13 @@
         <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4618,13 +4598,13 @@
         <v>20330051920132</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4641,13 +4621,13 @@
         <v>20330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4661,22 +4641,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920141</v>
+        <v>20330051920145</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4684,22 +4664,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920141</v>
+        <v>20330051920145</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4707,22 +4687,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920145</v>
+        <v>20330051920129</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4730,16 +4710,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920145</v>
+        <v>20330051920141</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -4753,16 +4733,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -4779,90 +4759,44 @@
         <v>20330051920148</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920129</v>
+        <v>19330051920145</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>58</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920387</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920145</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -185,16 +185,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>González Nuñez Veronica</t>
@@ -992,7 +992,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1001,10 +1001,10 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1069,7 +1069,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1078,16 +1078,16 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>10</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1096,7 +1096,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1146,7 +1146,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1155,10 +1155,10 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1232,16 +1232,16 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>5</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1250,10 +1250,10 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1300,7 +1300,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1309,16 +1309,16 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1327,10 +1327,10 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1371,13 +1371,13 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1386,16 +1386,16 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1407,7 +1407,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1430,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -1448,13 +1448,13 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1463,16 +1463,16 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>5</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1484,7 +1484,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1531,7 +1531,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1540,10 +1540,10 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1608,7 +1608,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1617,10 +1617,10 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1635,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1685,7 +1685,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1694,16 +1694,16 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>9</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1715,7 +1715,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1762,7 +1762,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1771,10 +1771,10 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1789,7 +1789,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1839,7 +1839,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1848,10 +1848,10 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1916,7 +1916,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1925,10 +1925,10 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1946,7 +1946,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1993,7 +1993,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2002,16 +2002,16 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2023,7 +2023,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2070,7 +2070,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2079,10 +2079,10 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2100,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2141,13 +2141,13 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2156,16 +2156,16 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2174,10 +2174,10 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2224,7 +2224,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2233,10 +2233,10 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2251,10 +2251,10 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2301,7 +2301,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2310,16 +2310,16 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2372,13 +2372,13 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2387,16 +2387,16 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>5</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2408,7 +2408,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2455,7 +2455,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2464,10 +2464,10 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2485,7 +2485,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2532,7 +2532,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2541,16 +2541,16 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2559,10 +2559,10 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2609,7 +2609,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2618,10 +2618,10 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2686,7 +2686,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2695,10 +2695,10 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2763,7 +2763,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2772,10 +2772,10 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2793,7 +2793,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2840,7 +2840,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2849,10 +2849,10 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2867,10 +2867,10 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2917,7 +2917,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2926,10 +2926,10 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2947,7 +2947,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2994,7 +2994,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3003,10 +3003,10 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3071,7 +3071,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3080,10 +3080,10 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3148,7 +3148,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3157,10 +3157,10 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3175,7 +3175,7 @@
         <v>7</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3225,7 +3225,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3234,16 +3234,16 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>8</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3252,10 +3252,10 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3296,13 +3296,13 @@
         <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3311,10 +3311,10 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3329,7 +3329,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3388,10 +3388,10 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3409,7 +3409,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3450,13 +3450,13 @@
         <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3465,10 +3465,10 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3483,7 +3483,7 @@
         <v>5</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3583,28 +3583,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>70.59</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G2">
-        <v>29.41</v>
+        <v>14.29</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3">
         <v>35</v>
@@ -3636,7 +3636,7 @@
         <v>14.29</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3656,30 +3656,30 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>85.70999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="G4">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3688,19 +3688,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>91.18000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="G5">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3711,34 +3711,34 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>91.43000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3752,25 +3752,25 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3780,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3824,67 +3824,47 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920122</v>
+        <v>20330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920135</v>
+        <v>19330051920145</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920145</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3932,7 +3912,7 @@
         <v>70</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4517,7 +4497,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4549,22 +4529,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920126</v>
+        <v>20330051920119</v>
       </c>
       <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" t="s">
-        <v>79</v>
-      </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4572,19 +4552,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920126</v>
+        <v>20330051920119</v>
       </c>
       <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
         <v>80</v>
       </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -4595,22 +4575,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920132</v>
+        <v>20330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4618,19 +4598,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920132</v>
+        <v>20330051920151</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
@@ -4641,22 +4621,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920145</v>
+        <v>20330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4664,19 +4644,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920145</v>
+        <v>20330051920132</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
@@ -4687,116 +4667,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920129</v>
+        <v>19330051920145</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920141</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920387</v>
-      </c>
-      <c r="B10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" t="s">
-        <v>124</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920148</v>
-      </c>
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920145</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20212.xlsx
+++ b/grupos/4ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -185,21 +185,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,262 +212,262 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
     <t>CERVANTES</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
     <t>JAVIER</t>
   </si>
   <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
     <t>ESMERALDA</t>
   </si>
   <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>DIANA VIANNEY</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
     <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
   </si>
 </sst>
 </file>
@@ -989,16 +989,16 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -1013,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1066,16 +1066,16 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1143,16 +1143,16 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -1220,16 +1220,16 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -1238,16 +1238,16 @@
         <v>7</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>7</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1297,16 +1297,16 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1315,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1362,7 +1362,7 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -1374,16 +1374,16 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>8</v>
@@ -1392,13 +1392,13 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>7</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1421,7 +1421,7 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1439,7 +1439,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>6</v>
@@ -1451,16 +1451,16 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -1469,16 +1469,16 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1528,16 +1528,16 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1546,7 +1546,7 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1605,16 +1605,16 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1632,7 +1632,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1682,16 +1682,16 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -1747,7 +1747,7 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -1759,16 +1759,16 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -1777,13 +1777,13 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>8</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1836,16 +1836,16 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>8</v>
@@ -1854,7 +1854,7 @@
         <v>8</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1913,16 +1913,16 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>9</v>
@@ -1931,7 +1931,7 @@
         <v>7</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1990,16 +1990,16 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -2014,7 +2014,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2067,16 +2067,16 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>9</v>
@@ -2132,7 +2132,7 @@
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -2144,16 +2144,16 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2162,7 +2162,7 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2171,7 +2171,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2221,16 +2221,16 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>9</v>
@@ -2239,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2248,7 +2248,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2298,16 +2298,16 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2322,10 +2322,10 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2345,7 +2345,7 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2363,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>5</v>
@@ -2375,16 +2375,16 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>5</v>
@@ -2393,16 +2393,16 @@
         <v>6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2452,16 +2452,16 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -2479,7 +2479,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2529,16 +2529,16 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2547,7 +2547,7 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2606,16 +2606,16 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -2683,16 +2683,16 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2760,16 +2760,16 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -2787,7 +2787,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2837,16 +2837,16 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -2861,7 +2861,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2914,16 +2914,16 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -2938,7 +2938,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -2991,16 +2991,16 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -3068,16 +3068,16 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -3095,7 +3095,7 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3145,16 +3145,16 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>8</v>
@@ -3163,7 +3163,7 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3222,16 +3222,16 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>7</v>
@@ -3287,7 +3287,7 @@
         <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>8</v>
@@ -3299,16 +3299,16 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>9</v>
@@ -3317,16 +3317,16 @@
         <v>8</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>6</v>
@@ -3376,16 +3376,16 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -3453,16 +3453,16 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>9</v>
@@ -3471,16 +3471,16 @@
         <v>8</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>7</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3497,7 +3497,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>5</v>
@@ -3506,28 +3506,28 @@
         <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3583,28 +3583,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>85.70999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G2">
-        <v>14.29</v>
+        <v>5.88</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3615,28 +3615,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>85.70999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="G3">
-        <v>14.29</v>
+        <v>2.94</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3650,57 +3650,57 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>35</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>91.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>34</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3711,28 +3711,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3743,16 +3743,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3780,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3805,66 +3805,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920122</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920135</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920145</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3900,64 +3840,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920122</v>
+        <v>20330051920115</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920135</v>
+        <v>20330051920116</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920145</v>
+        <v>20330051920118</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920115</v>
+        <v>20330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
         <v>121</v>
@@ -3968,13 +3908,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920116</v>
+        <v>20330051920121</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>122</v>
@@ -3985,13 +3925,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920118</v>
+        <v>20330051920122</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>123</v>
@@ -4002,13 +3942,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920119</v>
+        <v>20330051920123</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>124</v>
@@ -4019,13 +3959,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920121</v>
+        <v>20330051920124</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>125</v>
@@ -4036,13 +3976,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920123</v>
+        <v>20330051920125</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
         <v>126</v>
@@ -4053,13 +3993,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920124</v>
+        <v>20330051920126</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
         <v>127</v>
@@ -4070,13 +4010,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920125</v>
+        <v>20330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>128</v>
@@ -4087,16 +4027,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920126</v>
+        <v>20330051920128</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4104,16 +4044,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920127</v>
+        <v>20330051920129</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4121,16 +4061,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920128</v>
+        <v>20330051920131</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4138,16 +4078,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920129</v>
+        <v>20330051920132</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4155,16 +4095,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920131</v>
+        <v>20330051920133</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4172,16 +4112,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920132</v>
+        <v>20330051920134</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4189,16 +4129,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920133</v>
+        <v>20330051920135</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4206,13 +4146,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920134</v>
+        <v>20330051920136</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
         <v>135</v>
@@ -4223,13 +4163,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920136</v>
+        <v>20330051920137</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
@@ -4240,13 +4180,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920137</v>
+        <v>20330051920139</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>137</v>
@@ -4257,13 +4197,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
         <v>138</v>
@@ -4274,16 +4214,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4291,16 +4231,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920140</v>
+        <v>20330051920141</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4308,13 +4248,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920141</v>
+        <v>20330051920389</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4325,13 +4265,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920389</v>
+        <v>20330051920142</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4342,13 +4282,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920142</v>
+        <v>20330051920143</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4359,13 +4299,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920143</v>
+        <v>20330051920144</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4376,16 +4316,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920144</v>
+        <v>20330051920387</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4393,16 +4333,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920387</v>
+        <v>20330051920145</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4410,13 +4350,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920145</v>
+        <v>20330051920148</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -4427,13 +4367,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920148</v>
+        <v>20330051920150</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4444,13 +4384,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920150</v>
+        <v>20330051920151</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -4461,13 +4401,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920151</v>
+        <v>20330051920153</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -4478,10 +4415,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920153</v>
+        <v>19330051920145</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
+        <v>117</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -4497,7 +4437,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4529,22 +4469,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4552,19 +4492,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920119</v>
+        <v>20330051920122</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -4575,19 +4515,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920151</v>
+        <v>20330051920135</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -4598,94 +4538,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920151</v>
+        <v>19330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920132</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920145</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
